--- a/backend/excel-templates/bachelor_upload_test_data.xlsx
+++ b/backend/excel-templates/bachelor_upload_test_data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,9 +416,12 @@
         <v>Batch</v>
       </c>
       <c r="F1" t="str">
+        <v>Cluster</v>
+      </c>
+      <c r="G1" t="str">
         <v>Supervisor</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>External Examiner</v>
       </c>
     </row>
@@ -439,9 +442,12 @@
         <v>078</v>
       </c>
       <c r="F2" t="str">
+        <v>AIML</v>
+      </c>
+      <c r="G2" t="str">
         <v>Dr. Ram Acharya</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>Prof. Hari Bhandari</v>
       </c>
     </row>
@@ -462,9 +468,12 @@
         <v>078</v>
       </c>
       <c r="F3" t="str">
+        <v>IPCV</v>
+      </c>
+      <c r="G3" t="str">
         <v>Prof. Sita Sharma</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Dr. Sagar Ojha</v>
       </c>
     </row>
@@ -485,9 +494,12 @@
         <v>078</v>
       </c>
       <c r="F4" t="str">
+        <v>ANLP</v>
+      </c>
+      <c r="G4" t="str">
         <v>Assoc. Prof. Krishna Poudel</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
@@ -508,9 +520,12 @@
         <v>078</v>
       </c>
       <c r="F5" t="str">
+        <v>NTS</v>
+      </c>
+      <c r="G5" t="str">
         <v>Dr. Gita Rai</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>Dr. Umesh Lama</v>
       </c>
     </row>
@@ -531,9 +546,12 @@
         <v>078</v>
       </c>
       <c r="F6" t="str">
+        <v>EDMES</v>
+      </c>
+      <c r="G6" t="str">
         <v>Prof. Mohan Adhikari</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Prof. Sunita Acharya</v>
       </c>
     </row>
@@ -554,9 +572,12 @@
         <v>078</v>
       </c>
       <c r="F7" t="str">
+        <v>ACOM</v>
+      </c>
+      <c r="G7" t="str">
         <v>Dr. Bishnu Basnet</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>Dr. Roshan Karki</v>
       </c>
     </row>
@@ -577,9 +598,12 @@
         <v>078</v>
       </c>
       <c r="F8" t="str">
+        <v>EII</v>
+      </c>
+      <c r="G8" t="str">
         <v>Dr. Ram Acharya</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>Prof. Hari Bhandari</v>
       </c>
     </row>
@@ -600,9 +624,12 @@
         <v>078</v>
       </c>
       <c r="F9" t="str">
+        <v>AIML</v>
+      </c>
+      <c r="G9" t="str">
         <v>Prof. Sita Sharma</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>Dr. Sagar Ojha</v>
       </c>
     </row>
@@ -623,9 +650,12 @@
         <v>078</v>
       </c>
       <c r="F10" t="str">
+        <v>IPCV</v>
+      </c>
+      <c r="G10" t="str">
         <v>Assoc. Prof. Krishna Poudel</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
@@ -646,9 +676,12 @@
         <v>078</v>
       </c>
       <c r="F11" t="str">
+        <v>ANLP</v>
+      </c>
+      <c r="G11" t="str">
         <v>Dr. Gita Rai</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>Dr. Umesh Lama</v>
       </c>
     </row>
@@ -669,9 +702,12 @@
         <v>078</v>
       </c>
       <c r="F12" t="str">
+        <v>NTS</v>
+      </c>
+      <c r="G12" t="str">
         <v>Prof. Mohan Adhikari</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>Prof. Sunita Acharya</v>
       </c>
     </row>
@@ -692,9 +728,12 @@
         <v>078</v>
       </c>
       <c r="F13" t="str">
+        <v>EDMES</v>
+      </c>
+      <c r="G13" t="str">
         <v>Dr. Bishnu Basnet</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>Dr. Roshan Karki</v>
       </c>
     </row>
@@ -715,9 +754,12 @@
         <v>078</v>
       </c>
       <c r="F14" t="str">
+        <v>ACOM</v>
+      </c>
+      <c r="G14" t="str">
         <v>Dr. Ram Acharya</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>Prof. Hari Bhandari</v>
       </c>
     </row>
@@ -738,9 +780,12 @@
         <v>078</v>
       </c>
       <c r="F15" t="str">
+        <v>EII</v>
+      </c>
+      <c r="G15" t="str">
         <v>Prof. Sita Sharma</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>Dr. Sagar Ojha</v>
       </c>
     </row>
@@ -761,9 +806,12 @@
         <v>078</v>
       </c>
       <c r="F16" t="str">
+        <v>AIML</v>
+      </c>
+      <c r="G16" t="str">
         <v>Assoc. Prof. Krishna Poudel</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>Assoc. Prof. Rita Maharjan</v>
       </c>
     </row>
@@ -784,9 +832,12 @@
         <v>078</v>
       </c>
       <c r="F17" t="str">
+        <v>IPCV</v>
+      </c>
+      <c r="G17" t="str">
         <v>Dr. Gita Rai</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
         <v>Dr. Umesh Lama</v>
       </c>
     </row>
@@ -807,9 +858,12 @@
         <v>078</v>
       </c>
       <c r="F18" t="str">
+        <v>ANLP</v>
+      </c>
+      <c r="G18" t="str">
         <v>Prof. Mohan Adhikari</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>Prof. Sunita Acharya</v>
       </c>
     </row>
@@ -830,9 +884,12 @@
         <v>078</v>
       </c>
       <c r="F19" t="str">
+        <v>NTS</v>
+      </c>
+      <c r="G19" t="str">
         <v>Dr. Bishnu Basnet</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>Dr. Roshan Karki</v>
       </c>
     </row>
@@ -853,9 +910,12 @@
         <v>078</v>
       </c>
       <c r="F20" t="str">
+        <v>EDMES</v>
+      </c>
+      <c r="G20" t="str">
         <v>Dr. Ram Acharya</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>Prof. Hari Bhandari</v>
       </c>
     </row>
@@ -876,9 +936,12 @@
         <v>078</v>
       </c>
       <c r="F21" t="str">
+        <v>ACOM</v>
+      </c>
+      <c r="G21" t="str">
         <v>Prof. Sita Sharma</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>Dr. Sagar Ojha</v>
       </c>
     </row>
@@ -899,9 +962,12 @@
         <v>078</v>
       </c>
       <c r="F22" t="str">
+        <v>EII</v>
+      </c>
+      <c r="G22" t="str">
         <v>Assoc. Prof. Krishna Poudel</v>
       </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v/>
       </c>
     </row>
@@ -922,9 +988,12 @@
         <v>078</v>
       </c>
       <c r="F23" t="str">
+        <v>AIML</v>
+      </c>
+      <c r="G23" t="str">
         <v>Dr. Gita Rai</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v/>
       </c>
     </row>
@@ -945,9 +1014,12 @@
         <v>078</v>
       </c>
       <c r="F24" t="str">
+        <v>IPCV</v>
+      </c>
+      <c r="G24" t="str">
         <v>Prof. Mohan Adhikari</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
         <v/>
       </c>
     </row>
@@ -968,9 +1040,12 @@
         <v>078</v>
       </c>
       <c r="F25" t="str">
+        <v>ANLP</v>
+      </c>
+      <c r="G25" t="str">
         <v>Dr. Bishnu Basnet</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v/>
       </c>
     </row>
@@ -991,9 +1066,12 @@
         <v>078</v>
       </c>
       <c r="F26" t="str">
+        <v>NTS</v>
+      </c>
+      <c r="G26" t="str">
         <v>Dr. Ram Acharya</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v/>
       </c>
     </row>
@@ -1014,9 +1092,12 @@
         <v>078</v>
       </c>
       <c r="F27" t="str">
-        <v/>
+        <v>EDMES</v>
       </c>
       <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
         <v/>
       </c>
     </row>
@@ -1037,9 +1118,12 @@
         <v>078</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>ACOM</v>
       </c>
       <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
         <v/>
       </c>
     </row>
@@ -1060,9 +1144,12 @@
         <v>078</v>
       </c>
       <c r="F29" t="str">
-        <v/>
+        <v>EII</v>
       </c>
       <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
         <v/>
       </c>
     </row>
@@ -1083,9 +1170,12 @@
         <v>078</v>
       </c>
       <c r="F30" t="str">
-        <v/>
+        <v>AIML</v>
       </c>
       <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
         <v/>
       </c>
     </row>
@@ -1106,15 +1196,18 @@
         <v>078</v>
       </c>
       <c r="F31" t="str">
-        <v/>
+        <v>IPCV</v>
       </c>
       <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H31"/>
   </ignoredErrors>
 </worksheet>
 </file>